--- a/artfynd/S 4746-2024 artfynd.xlsx
+++ b/artfynd/S 4746-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY133"/>
+  <dimension ref="A1:AZ133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127813609</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109304291</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109305398</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109308244</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109308646</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109781116</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109792551</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109792998</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109793265</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109794018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117416</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127813522</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2032,6 +2097,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127815861</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2129,6 +2199,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127817684</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108716336</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2345,6 +2425,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109304299</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2453,6 +2538,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109304907</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2561,6 +2651,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109305386</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2669,6 +2764,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109306089</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2777,6 +2877,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109307561</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2885,6 +2990,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109308248</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2982,6 +3092,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737750</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3080,6 +3195,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776252</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3188,6 +3308,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776930</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3296,6 +3421,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109778545</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3404,6 +3534,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109781138</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3512,6 +3647,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109781786</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3620,6 +3760,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783110</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3728,6 +3873,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783224</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3836,6 +3986,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783243</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3944,6 +4099,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783391</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4052,6 +4212,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783441</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4160,6 +4325,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783502</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4268,6 +4438,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109786124</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4376,6 +4551,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109789026</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4484,6 +4664,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109791496</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4592,6 +4777,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109792523</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4700,6 +4890,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109792620</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4808,6 +5003,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109792992</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4905,6 +5105,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429119</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5002,6 +5207,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429136</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5099,6 +5309,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117424</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5196,6 +5411,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127815952</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5293,6 +5513,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127816039</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5390,6 +5615,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127817757</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5487,6 +5717,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128028361</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5584,6 +5819,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128032747</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5681,6 +5921,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128037156</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5789,6 +6034,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109305384</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5886,6 +6136,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117410</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5983,6 +6238,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127815946</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6080,6 +6340,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127817617</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6188,6 +6453,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109781122</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6285,6 +6555,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737749</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6393,6 +6668,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783117</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6501,6 +6781,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109791492</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6598,6 +6883,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128038007</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6695,6 +6985,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53888249</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6803,6 +7098,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109304326</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6911,6 +7211,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109305139</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7019,6 +7324,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109308486</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7127,6 +7437,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776935</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7235,6 +7550,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109786146</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7343,6 +7663,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109786358</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7451,6 +7776,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109790949</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7548,6 +7878,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429118</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7645,6 +7980,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429125</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7742,6 +8082,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127812863</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7839,6 +8184,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128038346</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7936,6 +8286,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117822</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8044,6 +8399,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109307254</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8142,6 +8502,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776112</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8240,6 +8605,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109778573</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8348,6 +8718,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109779952</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8456,6 +8831,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109781392</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8564,6 +8944,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783334</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8672,6 +9057,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109792226</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8769,6 +9159,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429127</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8866,6 +9261,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429135</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8963,6 +9363,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127816762</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9060,6 +9465,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127819757</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9157,6 +9567,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128028035</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9254,6 +9669,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117699</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9351,6 +9771,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429129</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9459,6 +9884,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109307243</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9556,6 +9986,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429126</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9653,6 +10088,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127817534</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9761,6 +10201,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108716415</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9858,6 +10303,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429131</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9955,6 +10405,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126120021</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10052,6 +10507,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109737751</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10160,6 +10620,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109792318</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10257,6 +10722,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429121</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10354,6 +10824,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429130</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10467,6 +10942,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109305624</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10580,6 +11060,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776227</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10693,6 +11178,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109781784</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10806,6 +11296,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108716004</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10909,6 +11404,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776580</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11012,6 +11512,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776912</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11125,6 +11630,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783527</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11238,6 +11748,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109792463</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11351,6 +11866,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109795269</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11458,6 +11978,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117298</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11565,6 +12090,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126120258</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11672,6 +12202,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820637</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11779,6 +12314,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128026019</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11886,6 +12426,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128037243</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11993,6 +12538,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128038205</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12095,6 +12645,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127820503</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12197,6 +12752,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128037598</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12298,6 +12858,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429138</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12395,6 +12960,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117351</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12492,6 +13062,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127816027</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12600,6 +13175,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109305893</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12698,6 +13278,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776318</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12800,6 +13385,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776453</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12898,6 +13488,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776644</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13000,6 +13595,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109776776</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13098,6 +13698,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109778629</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13206,6 +13811,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109779255</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13318,6 +13928,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109779607</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13426,6 +14041,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109779664</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13538,6 +14158,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109779748</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13646,6 +14271,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783348</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13758,6 +14388,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109785398</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13866,6 +14501,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109786379</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13974,6 +14614,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109791348</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14082,6 +14727,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109791431</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14190,6 +14840,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109793347</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14287,6 +14942,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111429140</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14388,8 +15048,147 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127815966</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>